--- a/output/change-management/claude/sample-1/workpaper.xlsx
+++ b/output/change-management/claude/sample-1/workpaper.xlsx
@@ -1442,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:12:58.357525Z</t>
+          <t>2026-07-03T03:34:53.966142Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>4031</v>
+        <v>12210</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>1200</v>
+        <v>4050</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.114852</v>
+        <v>0.4869</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>14479</v>
+        <v>16818</v>
       </c>
     </row>
     <row r="3">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:13:13.294464Z</t>
+          <t>2026-07-03T03:35:39.656943Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-prior-to-deployment:sample-1</t>
+          <t>judge:approved-by-authorised-approver-pre-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -1558,185 +1558,45 @@
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>4107</v>
+        <v>12426</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>2638</v>
+        <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>1180</v>
+        <v>3666</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.114492</v>
+        <v>0.46134</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>14933</v>
+        <v>15463</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:27.897046Z</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>judge:pre-deployment-testing-evidence-retained:sample-1</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>4077</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>1221</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.117117</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>14599</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:41.440103Z</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>judge:change-request-documents-scope-risk-rollback:sample-2</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>3888</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.106782</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>13531</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:13:55.701453Z</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>judge:authorised-approver-prior-to-deployment:sample-2</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>3964</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>1057</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.103122</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>14259</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:14:09.625203Z</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>judge:pre-deployment-testing-evidence-retained:sample-2</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>3934</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>2638</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1141</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.108972</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>13920</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E8" s="20">
-        <f>SUM(E2:E7)</f>
+      <c r="E4" s="20">
+        <f>SUM(E2:E3)</f>
         <v/>
       </c>
-      <c r="F8" s="20">
-        <f>SUM(F2:F7)</f>
+      <c r="F4" s="20">
+        <f>SUM(F2:F3)</f>
         <v/>
       </c>
-      <c r="G8" s="20">
-        <f>SUM(G2:G7)</f>
+      <c r="G4" s="20">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
-      <c r="H8" s="21">
-        <f>SUM(H2:H7)</f>
+      <c r="H4" s="21">
+        <f>SUM(H2:H3)</f>
         <v/>
       </c>
-      <c r="I8" s="20">
-        <f>SUM(I2:I7)</f>
+      <c r="I4" s="20">
+        <f>SUM(I2:I3)</f>
         <v/>
       </c>
     </row>

--- a/output/change-management/claude/sample-1/workpaper.xlsx
+++ b/output/change-management/claude/sample-1/workpaper.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:13 UTC</t>
+          <t>03 Jul 2026, 03:42 UTC</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Production changes are approved by an authorised change approver prior to deployment”. Specifically: The change request records approval by Priya Nadkarni (a different named human from requester Marcus Bell) at 2026-06-23 15:42 UTC, before the 2026-06-24 20:00 UTC deployment window, and cites CAB-2026-W25.</t>
+          <t>Provide additional evidence to close “Production changes are approved by an authorised change approver prior to deployment”. Specifically: The change request names Priya Nadkarni (Change Approver, CAB) as approver, separate from requester Marcus Bell, with an approval timestamp of 2026-06-23 15:42 UTC — before the 2026-06-24 20:00 UTC deployment window.</t>
         </is>
       </c>
     </row>
@@ -884,19 +884,21 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>The change request CHG-2026-0847 satisfies every testable criterion: identifier follows CHG-YYYY-NNNN format; scope enumerates affected systems (payments-primary RDS, payments-api) and repository (infra-terraform PR #2411); risk is classified Medium; a three-step rollback plan with RTO is documented; named requester (Marcus Bell) and approver (Priya Nadkarni) are given; planned start/end window is 2026-06-24 20:00–22:00 UTC; and the change is categorised as Normal. This attribute concerns documentation completeness only — approval validity/independence is judged separately.</t>
+          <t>Change request CHG-2026-0847 exists and satisfies every documentation criterion: identifier follows CHG-YYYY-NNNN format; scope lists systems (payments-primary RDS, payments-api) and repo (northpeak/infra-terraform PR #2411); risk classified Medium; rollback plan has three concrete steps with validated RTO; named requester (Marcus Bell) and named approver (Priya Nadkarni); planned window 2026-06-24 20:00–22:00 UTC; category Normal. Change targets production payments cluster, so no out-of-scope exception applies.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only exception rejected — this is a Postgres major version upgrade on a production cluster, not documentation.</t>
+          <t>Documentation-only exception: rejected — change alters production Postgres cluster and application code.
+Dev/staging exception: rejected — target is payments-primary production RDS.
+Incident Response hotfix: rejected — planned Normal change with CAB approval, not break-fix.</t>
         </is>
       </c>
     </row>
@@ -916,7 +918,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The change request records approval by Priya Nadkarni (a different named human from requester Marcus Bell) at 2026-06-23 15:42 UTC, before the 2026-06-24 20:00 UTC deployment window, and cites CAB-2026-W25. However, this is a Normal change requiring 2 approvers (Change Coordinator + Change Approver from CAB); only one approver (the CAB Change Approver) is named — no Change Coordinator approval is evidenced. Additionally, the signed CAB minutes (`cab-minutes-w25.pdf`) and IdP role membership confirming Priya holds the Change Approver role are not included in this bundle. Providing the CAB minutes showing a second approver / Change Coordinator sign-off, and an IdP export confirming Priya's Change Approver role, would resolve to SUCCESS.</t>
+          <t>The change request names Priya Nadkarni (Change Approver, CAB) as approver, separate from requester Marcus Bell, with an approval timestamp of 2026-06-23 15:42 UTC — before the 2026-06-24 20:00 UTC deployment window. The deployment log independently corroborates this approval. However, this is a Normal change requiring 2 approvers (Change Coordinator + Change Approver from CAB); only Priya (CAB Approver) is documented — no Change Coordinator approval is shown. Additionally, the signed CAB minutes (`cab-minutes-w25.pdf`) evidencing CAB review are explicitly not included in the bundle, and the IdP role assignment for Priya as Change Approver is not provided. Providing the CAB minutes, an IdP role listing confirming Priya's Change Approver role, and evidence of a second Change Coordinator approval would resolve this to SUCCESS.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
@@ -924,8 +926,8 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only / dev-staging exception — rejected: this change modifies production payments-primary RDS and payments-api.
-Emergency retrospective approval — not applicable: change is categorised Normal and approval is pre-deployment.</t>
+          <t>Documentation-only exception — rejected; this is a Postgres major-version upgrade on a production cluster, clearly in-scope.
+Emergency retrospective approval — not applicable; change is classified Normal and approval is pre-deployment.</t>
         </is>
       </c>
     </row>
@@ -945,16 +947,16 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Change is Normal category. A test plan and test results are attached via pre-deployment-test-results.xlsx, referenced in the change request. Test execution timestamps (2026-06-23 14:12–14:14) predate the deployment window start (2026-06-24 20:00 UTC). Functional smoke tests of the affected payments API surface (healthz, ledger insert/read, monotonic constraint, currency conversion) are present and all PASS, so the failed-test-blocks-deployment criterion is not triggered. Emergency criteria are N/A.</t>
+          <t>Change is Normal category and has both a test plan and test results attached (pre-deployment-test-results.xlsx referenced in the change request, listing 42 planned test cases including 12 functional smoke tests). All sampled functional smoke tests executed on 2026-06-23, prior to the deployment window opening on 2026-06-24 20:00 UTC. All sampled results show PASS; no failed tests observed that would block deployment. Emergency-change criteria are not applicable.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Emergency post-deployment testing clause: not applicable — change is Normal, not Emergency.
-Documentation-only exception: not applicable — change involves Postgres major version upgrade and library bump.</t>
+          <t>Emergency-change post-deployment verification (within 24h) criterion — rejected as inapplicable because the change is categorised Normal.
+Failed-test / accepted-risk criterion — not triggered; all sampled test results are PASS.</t>
         </is>
       </c>
     </row>
@@ -969,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1013,12 +1015,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Title line</t>
+          <t>Header line</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Identifier 'CHG-2026-0847' present, matching CHG-YYYY-NNNN format.</t>
+          <t>Title reads 'CHG-2026-0847 — Upgrade Postgres 15 → 16 on payments-primary cluster' — identifier matches CHG-YYYY-NNNN format.</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1037,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Header block (Category/Risk/Systems/Repositories/Planned window)</t>
+          <t>Category/Risk/Systems header block</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Category: Normal; Risk: Medium; Systems affected: payments-primary (RDS), payments-api; Repositories touched: northpeak/infra-terraform PR #2411; Planned window: 2026-06-24 20:00 UTC → 22:00 UTC.</t>
+          <t>Category: Normal; Risk: Medium; Systems affected: payments-primary (RDS), payments-api; Repositories touched: northpeak/infra-terraform PR #2411; Planned window 2026-06-24 20:00–22:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1064,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Enumerates Postgres 15.7→16.3 upgrade, pg library bump 8.11→8.13, no schema changes.</t>
+          <t>Documents Postgres 15.7→16.3 upgrade and pg library bump 8.11→8.13, no schema changes.</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Three-step rollback: PITR snapshot restore, redeploy pinned pg@8.11, verify via /healthz and canary. RTO 25 min, validated in staging drill 2026-06-19.</t>
+          <t>Three-step rollback with snapshot ID snap-payments-2026-06-24-1955, redeploy pinned pg@8.11, health verification; RTO 25 min validated in staging drill 2026-06-19.</t>
         </is>
       </c>
     </row>
@@ -1101,19 +1103,19 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Requester section</t>
+          <t>Requester and Approver sections</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Named requester: Marcus Bell (Platform Engineer).</t>
+          <t>Named requester Marcus Bell (Platform Engineer); named approver Priya Nadkarni (Change Approver, CAB).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Every production change has a corresponding change request that documents scope, risk classification, and rollback plan</t>
+          <t>Production changes are approved by an authorised change approver prior to deployment</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
@@ -1123,12 +1125,12 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Approver section</t>
+          <t>Category / Approver / Approval record sections</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Named approver: Priya Nadkarni (Change Approver, CAB).</t>
+          <t>Category is 'Normal'; approver named as Priya Nadkarni (Change Approver, CAB); approval timestamp 2026-06-23 15:42 UTC noted as before deployment window; CAB reference CAB-2026-W25 cited; signed CAB minutes referenced as `cab-minutes-w25.pdf` but explicitly 'not included in this evidence bundle'. Only one approver is listed — no Change Coordinator approval documented.</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1147,12 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Category / Requester / Approver / Approval record sections</t>
+          <t>Requester section</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Category = Normal; Requester = Marcus Bell; Approver = Priya Nadkarni (Change Approver, CAB); Approval timestamp 2026-06-23 15:42 UTC; CAB reference CAB-2026-W25; signed CAB minutes noted as not included in bundle.</t>
+          <t>Requester is Marcus Bell (Platform Engineer), distinct human from approver Priya Nadkarni — four-eyes principle satisfied on the recorded approver.</t>
         </is>
       </c>
     </row>
@@ -1162,39 +1164,39 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Planned window</t>
+          <t>Line at 2026-06-24 20:00:15 UTC</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Deployment window 2026-06-24 20:00 UTC → 22:00 UTC — approval timestamp precedes window opening by ~28 hours.</t>
+          <t>Runner logs 'approval OK — CHG-2026-0847 approved by priya.nadkarni at 2026-06-23T15:42:00Z (CAB-2026-W25)', corroborating the approval timestamp precedes the 20:00:02 UTC deployment window start.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Pre-deployment testing is completed and evidence retained before release</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>deployment-log.txt</t>
+          <t>change-request.md</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>line at 2026-06-24 20:00:15 UTC</t>
+          <t>Testing evidence section</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Runner verified 'approval OK — CHG-2026-0847 approved by priya.nadkarni at 2026-06-23T15:42:00Z (CAB-2026-W25)'; only a single approver identity referenced.</t>
+          <t>References pre-deployment-test-results.xlsx with 42 planned test cases: 12 functional smoke, 24 regression, 6 rollback validation — all pass on staging.</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1213,12 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Header — Category</t>
+          <t>Header — Category / Planned window</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Change is classified as Normal, Risk Medium — invokes Standard/Normal testing criteria.</t>
+          <t>Change is Normal category; planned deployment window 2026-06-24 20:00–22:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1230,17 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>pre-deployment-test-results.xlsx</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Testing evidence section</t>
+          <t>Test Cases!A1:F13</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>References pre-deployment-test-results.xlsx with 42 test cases including 12 functional smoke, 24 regression, 6 rollback validation — all pass on staging.</t>
+          <t>Sheet contains 12 rows of test cases with columns Test ID, Category, Description, Result, Executed By, Executed At. Sampled rows TC-001 through TC-005 are Functional smoke tests covering payments API /healthz, ledger insert/read, transaction id constraint, and currency conversion — all Result=PASS, executed 2026-06-23 14:12–14:14 by test-bot.</t>
         </is>
       </c>
     </row>
@@ -1250,61 +1252,17 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-test-results.xlsx</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Test Cases!A1:F13</t>
+          <t>window start line</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>12 test rows with Test ID, Category=Functional, Description, Result=PASS, Executed By, Executed At. Sample rows TC-001..TC-005 cover payments API /healthz, ledger insert/read, transaction id monotonic constraint, and currency-conversion — functional smoke of affected surfaces.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>pre-deployment-test-results.xlsx</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Test Cases!F2:F6 (Executed At)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>Test execution timestamps 2026-06-23 14:12–14:14 UTC, which predate the deployment window start of 2026-06-24 20:00 UTC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>deployment-log.txt</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>window start line</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Deployment window began 2026-06-24 20:00:02 UTC — confirms tests (2026-06-23) predate deployment.</t>
+          <t>Deployment began 2026-06-24 20:00:02 UTC, which is after test execution on 2026-06-23 — testing dated prior to deployment.</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1335,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, authorised-approver-prior-to-deployment, authorised-approver-prior-to-deployment, pre-deployment-testing-evidence-retained, pre-deployment-testing-evidence-retained</t>
+          <t>change-request-documented, change-request-documented, change-request-documented, change-request-documented, change-request-documented, authorised-approver-pre-deployment, authorised-approver-pre-deployment, pre-deployment-testing-evidence, pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1360,7 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>authorised-approver-prior-to-deployment, pre-deployment-testing-evidence-retained</t>
+          <t>authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1385,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-testing-evidence-retained, pre-deployment-testing-evidence-retained</t>
+          <t>pre-deployment-testing-evidence</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1509,12 +1467,12 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:34:53.966142Z</t>
+          <t>2026-07-03T03:40:38.512115Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documents-scope-risk-rollback:sample-1</t>
+          <t>judge:change-request-documented:sample-1</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
@@ -1523,19 +1481,19 @@
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>12210</v>
+        <v>12237</v>
       </c>
       <c r="F2" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="16" t="n">
-        <v>4050</v>
+        <v>3945</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>0.4869</v>
+        <v>0.47943</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>16818</v>
+        <v>16903</v>
       </c>
     </row>
     <row r="3">
@@ -1544,12 +1502,12 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:35:39.656943Z</t>
+          <t>2026-07-03T03:41:38.676590Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:approved-by-authorised-approver-pre-deployment:sample-1</t>
+          <t>judge:authorised-approver-pre-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -1558,45 +1516,185 @@
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>12426</v>
+        <v>12282</v>
       </c>
       <c r="F3" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="16" t="n">
-        <v>3666</v>
+        <v>3635</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>0.46134</v>
+        <v>0.456855</v>
       </c>
       <c r="I3" s="16" t="n">
-        <v>15463</v>
+        <v>15711</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="20" t="inlineStr">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:42:20.425037Z</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>judge:pre-deployment-testing-evidence:sample-1</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>12171</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>3288</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>0.429165</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>14789</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:43:34.856033Z</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>judge:change-request-documented:sample-2</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>11808</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>3732</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>16764</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:44:17.557054Z</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>judge:authorised-approver-pre-deployment:sample-2</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>11853</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>3339</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>16002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T03:49:13.305734Z</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>judge:pre-deployment-testing-evidence:sample-2</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>11742</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>3528</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>264910</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E4" s="20">
-        <f>SUM(E2:E3)</f>
+      <c r="E8" s="20">
+        <f>SUM(E2:E7)</f>
         <v/>
       </c>
-      <c r="F4" s="20">
-        <f>SUM(F2:F3)</f>
+      <c r="F8" s="20">
+        <f>SUM(F2:F7)</f>
         <v/>
       </c>
-      <c r="G4" s="20">
-        <f>SUM(G2:G3)</f>
+      <c r="G8" s="20">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
-      <c r="H4" s="21">
-        <f>SUM(H2:H3)</f>
+      <c r="H8" s="21">
+        <f>SUM(H2:H7)</f>
         <v/>
       </c>
-      <c r="I4" s="20">
-        <f>SUM(I2:I3)</f>
+      <c r="I8" s="20">
+        <f>SUM(I2:I7)</f>
         <v/>
       </c>
     </row>

--- a/output/change-management/claude/sample-1/workpaper.xlsx
+++ b/output/change-management/claude/sample-1/workpaper.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:42 UTC</t>
+          <t>03 Jul 2026, 04:15 UTC</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Production changes are approved by an authorised change approver prior to deployment”. Specifically: The change request names Priya Nadkarni (Change Approver, CAB) as approver, separate from requester Marcus Bell, with an approval timestamp of 2026-06-23 15:42 UTC — before the 2026-06-24 20:00 UTC deployment window.</t>
+          <t>Provide additional evidence to close “Production changes are approved by an authorised change approver prior to deployment”. Specifically: Four-eyes is satisfied (requester Marcus Bell vs approver Priya Nadkarni are different named humans) and approval (2026-06-23 15:42 UTC) preceded the deployment window (2026-06-24 20:00 UTC), consistent with the deployment log.</t>
         </is>
       </c>
     </row>
@@ -884,21 +884,21 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Change request CHG-2026-0847 exists and satisfies every documentation criterion: identifier follows CHG-YYYY-NNNN format; scope lists systems (payments-primary RDS, payments-api) and repo (northpeak/infra-terraform PR #2411); risk classified Medium; rollback plan has three concrete steps with validated RTO; named requester (Marcus Bell) and named approver (Priya Nadkarni); planned window 2026-06-24 20:00–22:00 UTC; category Normal. Change targets production payments cluster, so no out-of-scope exception applies.</t>
+          <t>The change request CHG-2026-0847 exists and uses the CHG-YYYY-NNNN format. It documents scope (systems affected: payments-primary RDS + payments-api; repository northpeak/infra-terraform PR #2411; the Postgres 15.7→16.3 upgrade and pg library bump), a Medium risk classification, a detailed rollback plan (PITR snapshot, redeploy pinned library, canary verification, 25-min RTO), names requester Marcus Bell and approver Priya Nadkarni, and includes a planned window (2026-06-24 20:00→22:00 UTC). It is a Normal production change to the payments-primary cluster — not documentation-only, not an Incident Response hotfix, and not a dev/staging change — so it is in scope. Every criterion for this attribute is directly satisfied.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only exception: rejected — change alters production Postgres cluster and application code.
-Dev/staging exception: rejected — target is payments-primary production RDS.
-Incident Response hotfix: rejected — planned Normal change with CAB approval, not break-fix.</t>
+          <t>Documentation-only exception — rejected: change is a production Postgres major upgrade with infra code changes, not README/comment edits.
+Break-fix hotfix / Incident Response exception — rejected: CR is categorised Normal with pre-approved CAB window, not an emergency incident response.
+Dev/staging exception — rejected: deployment log and CR target production payments-primary cluster.</t>
         </is>
       </c>
     </row>
@@ -914,11 +914,11 @@
         </is>
       </c>
       <c r="C3" s="16" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The change request names Priya Nadkarni (Change Approver, CAB) as approver, separate from requester Marcus Bell, with an approval timestamp of 2026-06-23 15:42 UTC — before the 2026-06-24 20:00 UTC deployment window. The deployment log independently corroborates this approval. However, this is a Normal change requiring 2 approvers (Change Coordinator + Change Approver from CAB); only Priya (CAB Approver) is documented — no Change Coordinator approval is shown. Additionally, the signed CAB minutes (`cab-minutes-w25.pdf`) evidencing CAB review are explicitly not included in the bundle, and the IdP role assignment for Priya as Change Approver is not provided. Providing the CAB minutes, an IdP role listing confirming Priya's Change Approver role, and evidence of a second Change Coordinator approval would resolve this to SUCCESS.</t>
+          <t>Four-eyes is satisfied (requester Marcus Bell vs approver Priya Nadkarni are different named humans) and approval (2026-06-23 15:42 UTC) preceded the deployment window (2026-06-24 20:00 UTC), consistent with the deployment log. However, this is a Normal change, which requires at least 2 approvers (Change Coordinator + Change Approver from CAB); the change request names only one approver (Priya Nadkarni). The mandatory second Change Coordinator approver is not evidenced, and the CAB minutes proving CAB approval and Priya's Change Approver IdP role (cab-minutes-w25.pdf) are explicitly not in the bundle. Providing the signed CAB minutes showing a distinct Change Coordinator approval plus Priya's Change Approver role would resolve this to SUCCESS.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
@@ -926,8 +926,8 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Documentation-only exception — rejected; this is a Postgres major-version upgrade on a production cluster, clearly in-scope.
-Emergency retrospective approval — not applicable; change is classified Normal and approval is pre-deployment.</t>
+          <t>Policy 'Documentation-only' / dev-staging / incident-response exceptions — rejected, this is a production RDS upgrade classified Normal, not an exception case.
+Retrospective approval clause — not applicable; approval occurred before the window, so the change is not retrospective.</t>
         </is>
       </c>
     </row>
@@ -943,11 +943,11 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Change is Normal category and has both a test plan and test results attached (pre-deployment-test-results.xlsx referenced in the change request, listing 42 planned test cases including 12 functional smoke tests). All sampled functional smoke tests executed on 2026-06-23, prior to the deployment window opening on 2026-06-24 20:00 UTC. All sampled results show PASS; no failed tests observed that would block deployment. Emergency-change criteria are not applicable.</t>
+          <t>The change is classified Normal, so pre-deployment testing evidence (test plan + results) is required. The evidence bundle contains pre-deployment-test-results.xlsx with functional smoke test cases (TC-001–TC-005: /healthz, ledger insert/read, currency conversion) all marked PASS, satisfying the functional-smoke-of-affected-surfaces criterion. All tests passed (no failures to block deployment), and the test results were executed 2026-06-23 14:12–14:14 UTC — before the 2026-06-24 20:00 UTC deployment window — so evidence was retained before release. No tests failed, so the failure/accepted-risk criteria are not triggered.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
@@ -955,8 +955,8 @@
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Emergency-change post-deployment verification (within 24h) criterion — rejected as inapplicable because the change is categorised Normal.
-Failed-test / accepted-risk criterion — not triggered; all sampled test results are PASS.</t>
+          <t>Emergency post-deployment verification (24h) and accepted-risk criteria — rejected: change is Normal, not Emergency, and no tests failed.
+Documentation-only / staging-environment exception — rejected: this is a production Postgres major upgrade on the payments-primary cluster.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>Header line</t>
+          <t>Header + metadata block (CHG-2026-0847, Category/Risk/System(s) affected/Repositories touched/Planned window)</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Title reads 'CHG-2026-0847 — Upgrade Postgres 15 → 16 on payments-primary cluster' — identifier matches CHG-YYYY-NNNN format.</t>
+          <t>CR identifier CHG-2026-0847 in correct format; Category Normal; Risk Medium; systems payments-primary (RDS) and payments-api; repo northpeak/infra-terraform PR #2411; planned window 2026-06-24 20:00→22:00 UTC.</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Category/Risk/Systems header block</t>
+          <t>Scope and Rollback plan sections</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Category: Normal; Risk: Medium; Systems affected: payments-primary (RDS), payments-api; Repositories touched: northpeak/infra-terraform PR #2411; Planned window 2026-06-24 20:00–22:00 UTC.</t>
+          <t>Scope lists the Postgres 15.7→16.3 upgrade, pg@8.11→8.13 bump, no schema changes. Rollback plan gives PITR snapshot snap-payments-2026-06-24-1955, redeploy pinned to pg@8.11, canary verification, 25-min RTO validated in staging drill.</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Scope section</t>
+          <t>Requester and Approver sections</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Documents Postgres 15.7→16.3 upgrade and pg library bump 8.11→8.13, no schema changes.</t>
+          <t>Requester named Marcus Bell (Platform Engineer); Approver named Priya Nadkarni (Change Approver, CAB) — both distinct named humans.</t>
         </is>
       </c>
     </row>
@@ -1076,24 +1076,24 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Rollback plan section</t>
+          <t>Header (system / executor)</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Three-step rollback with snapshot ID snap-payments-2026-06-24-1955, redeploy pinned pg@8.11, health verification; RTO 25 min validated in staging drill 2026-06-19.</t>
+          <t>Deployment targets production payments-primary + payments-api, confirming this is an in-scope production change, not dev/staging or documentation-only.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Every production change has a corresponding change request that documents scope, risk classification, and rollback plan</t>
+          <t>Production changes are approved by an authorised change approver prior to deployment</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Requester and Approver sections</t>
+          <t>Category / Requester / Approver headings</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Named requester Marcus Bell (Platform Engineer); named approver Priya Nadkarni (Change Approver, CAB).</t>
+          <t>Category is 'Normal'; requester is Marcus Bell, approver is Priya Nadkarni (Change Approver, CAB) — two different named humans, but only one approver is listed where a Normal change requires two (Change Coordinator + Change Approver).</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Category / Approver / Approval record sections</t>
+          <t>Approval record section</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Category is 'Normal'; approver named as Priya Nadkarni (Change Approver, CAB); approval timestamp 2026-06-23 15:42 UTC noted as before deployment window; CAB reference CAB-2026-W25 cited; signed CAB minutes referenced as `cab-minutes-w25.pdf` but explicitly 'not included in this evidence bundle'. Only one approver is listed — no Change Coordinator approval documented.</t>
+          <t>Approval timestamp 2026-06-23 15:42 UTC (before window); CAB reference CAB-2026-W25; approval evidence is signed CAB minutes 'cab-minutes-w25.pdf' explicitly noted as NOT included in this evidence bundle.</t>
         </is>
       </c>
     </row>
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Requester section</t>
+          <t>window start line and 20:00:15 approval-OK line</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Requester is Marcus Bell (Platform Engineer), distinct human from approver Priya Nadkarni — four-eyes principle satisfied on the recorded approver.</t>
+          <t>Deployment window opened 2026-06-24 20:00:02 UTC; runner logged 'approval OK — approved by priya.nadkarni at 2026-06-23T15:42:00Z (CAB-2026-W25)', confirming approval preceded deployment but referencing only a single approver.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Production changes are approved by an authorised change approver prior to deployment</t>
+          <t>Pre-deployment testing is completed and evidence retained before release</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>deployment-log.txt</t>
+          <t>change-request.md</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Line at 2026-06-24 20:00:15 UTC</t>
+          <t>Header / Category field</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Runner logs 'approval OK — CHG-2026-0847 approved by priya.nadkarni at 2026-06-23T15:42:00Z (CAB-2026-W25)', corroborating the approval timestamp precedes the 20:00:02 UTC deployment window start.</t>
+          <t>CHG-2026-0847 is classified Category: Normal, Risk: Medium — triggering the pre-deployment test evidence requirement.</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>References pre-deployment-test-results.xlsx with 42 planned test cases: 12 functional smoke, 24 regression, 6 rollback validation — all pass on staging.</t>
+          <t>References pre-deployment-test-results.xlsx in the bundle; states 42 planned cases pass on staging including 12 functional smoke, 24 regression, 6 rollback validation.</t>
         </is>
       </c>
     </row>
@@ -1208,17 +1208,17 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>change-request.md</t>
+          <t>pre-deployment-test-results.xlsx</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Header — Category / Planned window</t>
+          <t>Test Cases!A2:F6 (TC-001 through TC-005)</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Change is Normal category; planned deployment window 2026-06-24 20:00–22:00 UTC.</t>
+          <t>Functional smoke tests of the payments API surface (healthz 200, ledger insert/read, monotonic constraint, currency conversion) all show Result=PASS, executed 2026-06-23 14:12–14:14 UTC.</t>
         </is>
       </c>
     </row>
@@ -1230,39 +1230,17 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-test-results.xlsx</t>
+          <t>deployment-log.txt</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Test Cases!A1:F13</t>
+          <t>window start line</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Sheet contains 12 rows of test cases with columns Test ID, Category, Description, Result, Executed By, Executed At. Sampled rows TC-001 through TC-005 are Functional smoke tests covering payments API /healthz, ledger insert/read, transaction id constraint, and currency conversion — all Result=PASS, executed 2026-06-23 14:12–14:14 by test-bot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Pre-deployment testing is completed and evidence retained before release</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>deployment-log.txt</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>window start line</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Deployment began 2026-06-24 20:00:02 UTC, which is after test execution on 2026-06-23 — testing dated prior to deployment.</t>
+          <t>Deployment window started 2026-06-24 20:00:02 UTC — after the 2026-06-23 test execution timestamps, confirming testing evidence existed and was retained before release.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1313,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>change-request-documented, change-request-documented, change-request-documented, change-request-documented, change-request-documented, authorised-approver-pre-deployment, authorised-approver-pre-deployment, pre-deployment-testing-evidence, pre-deployment-testing-evidence</t>
+          <t>change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, change-request-documents-scope-risk-rollback, approved-by-authorised-approver-before-deployment, approved-by-authorised-approver-before-deployment, pre-deployment-testing-completed-evidence-retained, pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1338,7 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>authorised-approver-pre-deployment, pre-deployment-testing-evidence</t>
+          <t>change-request-documents-scope-risk-rollback, approved-by-authorised-approver-before-deployment, pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1363,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>pre-deployment-testing-evidence</t>
+          <t>pre-deployment-testing-completed-evidence-retained</t>
         </is>
       </c>
     </row>
@@ -1467,33 +1445,33 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:40:38.512115Z</t>
+          <t>2026-07-03T04:15:27.645814Z</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documented:sample-1</t>
+          <t>judge:change-request-documents-scope-risk-rollback:sample-1</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
-        <v>12237</v>
+        <v>3704</v>
       </c>
       <c r="F2" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>1427</v>
+      </c>
+      <c r="H2" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="16" t="n">
-        <v>3945</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>0.47943</v>
-      </c>
       <c r="I2" s="16" t="n">
-        <v>16903</v>
+        <v>16785</v>
       </c>
     </row>
     <row r="3">
@@ -1502,33 +1480,33 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:41:38.676590Z</t>
+          <t>2026-07-03T04:15:41.510267Z</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-pre-deployment:sample-1</t>
+          <t>judge:approved-by-authorised-approver-before-deployment:sample-1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>12282</v>
+        <v>3732</v>
       </c>
       <c r="F3" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="H3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="16" t="n">
-        <v>3635</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0.456855</v>
-      </c>
       <c r="I3" s="16" t="n">
-        <v>15711</v>
+        <v>13863</v>
       </c>
     </row>
     <row r="4">
@@ -1537,33 +1515,33 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:42:20.425037Z</t>
+          <t>2026-07-03T04:15:54.852178Z</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>judge:pre-deployment-testing-evidence:sample-1</t>
+          <t>judge:pre-deployment-testing-completed-evidence-retained:sample-1</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>12171</v>
+        <v>3681</v>
       </c>
       <c r="F4" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="16" t="n">
-        <v>3288</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.429165</v>
-      </c>
       <c r="I4" s="16" t="n">
-        <v>14789</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="5">
@@ -1572,33 +1550,33 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:43:34.856033Z</t>
+          <t>2026-07-03T04:16:10.922021Z</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>judge:change-request-documented:sample-2</t>
+          <t>judge:change-request-documents-scope-risk-rollback:sample-2</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E5" s="16" t="n">
-        <v>11808</v>
+        <v>3561</v>
       </c>
       <c r="F5" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>1373</v>
+      </c>
+      <c r="H5" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="16" t="n">
-        <v>3732</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.45702</v>
-      </c>
       <c r="I5" s="16" t="n">
-        <v>16764</v>
+        <v>16054</v>
       </c>
     </row>
     <row r="6">
@@ -1607,33 +1585,33 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:44:17.557054Z</t>
+          <t>2026-07-03T04:16:23.637445Z</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>judge:authorised-approver-pre-deployment:sample-2</t>
+          <t>judge:approved-by-authorised-approver-before-deployment:sample-2</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>11853</v>
+        <v>3589</v>
       </c>
       <c r="F6" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>1115</v>
+      </c>
+      <c r="H6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="16" t="n">
-        <v>3339</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.42822</v>
-      </c>
       <c r="I6" s="16" t="n">
-        <v>16002</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="7">
@@ -1642,33 +1620,33 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-03T03:49:13.305734Z</t>
+          <t>2026-07-03T04:16:36.533739Z</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>judge:pre-deployment-testing-evidence:sample-2</t>
+          <t>judge:pre-deployment-testing-completed-evidence-retained:sample-2</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>claude-opus-4-7</t>
+          <t>claude-opus-4-8</t>
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>11742</v>
+        <v>3538</v>
       </c>
       <c r="F7" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>1089</v>
+      </c>
+      <c r="H7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="16" t="n">
-        <v>3528</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.44073</v>
-      </c>
       <c r="I7" s="16" t="n">
-        <v>264910</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="8">
